--- a/log/train_data_cat_clean.xlsx
+++ b/log/train_data_cat_clean.xlsx
@@ -463,11 +463,11 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>[31, 89, 94, 496, 558, 712, 813, 917, 1062, 1280]</t>
+          <t>[558, 917, 94, 31, 1062]</t>
         </is>
       </c>
     </row>
@@ -491,11 +491,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[18, 40, 53, 79, 103, 138, 145, 189, 331, 343, 421, 442, 455, 506, 570, 571, 583, 635, 729, 737, 739, 779, 780, 844, 887, 895, 898, 911, 914, 922, 941, 943, 944, 955, 956, 985, 1004, 1012, 1091, 1130, 1164, 1217, 1231, 1232, 1233, 1276, 1284, 1337, 1351, 1392, 1413, 1451]</t>
+          <t>[343, 780, 1232, 887, 941, 737, 138, 455, 18, 955, 145, 570, 1233, 583, 944, 1004, 844, 1276, 1231, 914, 956, 1130, 943, 779, 331, 1164, 40, 442, 922, 571, 1337, 421, 739, 1392, 103, 898, 1091, 895, 1413, 189, 729, 506]</t>
         </is>
       </c>
     </row>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[10, 49, 94, 126, 166, 247, 292, 301, 313, 336, 412, 489, 521, 536, 636, 638, 704, 706, 714, 822, 862, 970, 986, 1031, 1063, 1145, 1187, 1191, 1267, 1394, 1417]</t>
+          <t>[412, 970, 247, 714, 489, 313, 301, 126, 1031, 1267, 636, 1191, 1063, 94, 536, 10, 292, 1394, 336, 986, 521, 166, 822, 49]</t>
         </is>
       </c>
     </row>
@@ -543,11 +543,11 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>[57, 76, 146, 181, 194, 196, 226, 228, 233, 283, 349, 364, 431, 435, 484, 490, 501, 600, 632, 650, 656, 676, 759, 830, 838, 916, 960, 972, 976, 1030, 1039, 1043, 1089, 1092, 1158, 1161, 1192, 1220, 1237, 1292, 1359, 1379, 1450]</t>
+          <t>[1089, 146, 1220, 976, 1030, 484, 194, 233, 1379, 830, 1450, 916, 501, 181, 632, 1192, 650, 1092, 435, 600, 431, 759, 228, 349, 838, 1292, 676, 283, 490, 1039, 226, 364, 1158, 196, 972]</t>
         </is>
       </c>
     </row>
@@ -599,11 +599,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>[196, 411, 505, 676, 963, 1001, 1161]</t>
+          <t>[963, 676, 411, 505, 196, 1001]</t>
         </is>
       </c>
     </row>
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>[24, 76, 109, 190, 197, 262, 279, 305, 306, 317, 345, 350, 358, 378, 400, 422, 435, 475, 490, 491, 516, 523, 524, 592, 615, 619, 645, 650, 651, 674, 725, 731, 794, 818, 826, 876, 916, 974, 981, 984, 995, 1008, 1039, 1040, 1047, 1061, 1069, 1087, 1182, 1218, 1220, 1268, 1289, 1292, 1368, 1375, 1406, 1450, 1452, 1458]</t>
+          <t>[350, 1220, 1069, 1368, 1047, 1450, 523, 916, 279, 794, 674, 24, 306, 619, 475, 109, 876, 358, 197, 524, 262, 378, 650, 1406, 651, 984, 305, 826, 435, 491, 1375, 981, 818, 190, 1182, 974, 1292, 725, 1040, 490, 1039, 1452, 592, 422, 995]</t>
         </is>
       </c>
     </row>
@@ -655,11 +655,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>[4, 9, 12, 54, 174, 176, 329, 330, 349, 394, 414, 444, 459, 563, 572, 587, 658, 697, 706, 741, 750, 770, 785, 803, 873, 972, 1029, 1113, 1147, 1237, 1252, 1275, 1284, 1285, 1385, 1400, 1401, 1407]</t>
+          <t>[4, 1252, 394, 1147, 697, 1113, 12, 572, 54, 1029, 741, 176, 444, 1275, 658, 9, 587, 785, 459, 174, 1401, 563, 803, 349, 873, 1407, 750, 329, 330, 972]</t>
         </is>
       </c>
     </row>
@@ -683,11 +683,11 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>[15, 17, 20, 27, 29, 34, 38, 39, 41, 45, 55, 56, 67, 71, 74, 77, 81, 84, 91, 92, 100, 123, 129, 130, 131, 133, 137, 141, 143, 157, 172, 174, 192, 198, 208, 210, 216, 224, 231, 248, 254, 255, 261, 274, 287, 288, 295, 312, 325, 328, 331, 332, 340, 343, 347, 348, 367, 368, 369, 370, 374, 393, 398, 420, 425, 428, 447, 467, 468, 486, 487, 492, 494, 500, 510, 511, 513, 522, 527, 533, 538, 544, 557, 570, 571, 572, 575, 576, 581, 606, 616, 618, 626, 627, 628, 629, 630, 634, 643, 646, 647, 649, 657, 659, 663, 667, 675, 723, 726, 729, 737, 755, 761, 774, 798, 805, 807, 809, 814, 817, 831, 834, 835, 843, 844, 854, 864, 866, 871, 873, 874, 885, 887, 889, 890, 891, 896, 901, 902, 906, 911, 920, 932, 935, 947, 951, 968, 970, 971, 981, 993, 997, 1007, 1015, 1027, 1029, 1053, 1065, 1068, 1070, 1071, 1078, 1084, 1091, 1094, 1095, 1102, 1103, 1104, 1113, 1114, 1120, 1126, 1137, 1141, 1151, 1155, 1157, 1172, 1201, 1209, 1215, 1221, 1223, 1224, 1226, 1228, 1230, 1232, 1233, 1234, 1250, 1251, 1260, 1262, 1265, 1270, 1276, 1291, 1296, 1297, 1300, 1316, 1321, 1341, 1351, 1352, 1357, 1358, 1363, 1372, 1382, 1392, 1393, 1399, 1412, 1413, 1419, 1425, 1426, 1428, 1436, 1437, 1451, 1459]</t>
+          <t>[997, 970, 947, 198, 1078, 1084, 328, 45, 216, 343, 131, 1215, 557, 1232, 157, 248, 809, 287, 288, 805, 887, 1113, 513, 817, 737, 1104, 91, 1201, 130, 129, 1120, 492, 1224, 807, 572, 1094, 1221, 1296, 971, 1393, 92, 29, 570, 41, 1223, 55, 71, 646, 1233, 1007, 467, 1103, 814, 347, 1029, 1070, 1114, 1437, 1250, 522, 527, 1053, 581, 901, 544, 1071, 500, 487, 468, 192, 1226, 1341, 1425, 1270, 993, 951, 774, 844, 84, 891, 133, 137, 634, 1276, 393, 398, 1102, 667, 627, 332, 629, 889, 254, 1151, 1015, 331, 575, 1352, 1137, 538, 1428, 798, 77, 208, 1155, 15, 920, 843, 1382, 425, 1141, 1068, 831, 1316, 630, 123, 174, 494, 618, 1436, 675, 428, 56, 968, 647, 981, 210, 1260, 1265, 657, 1230, 1419, 835, 1426, 1357, 1157, 1372, 1209, 576, 896, 873, 1172, 935, 571, 1297, 368, 1228, 834, 890, 224, 1392, 274, 1399, 312, 261, 902, 20, 1363, 1091, 340, 81, 1413, 511, 1321, 1262, 723, 367, 932, 663, 864, 755, 643, 729, 885, 510, 486]</t>
         </is>
       </c>
     </row>
